--- a/data/trans_bre/P6903-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6903-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 24,51</t>
+          <t>-24,69; 24,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 52,74</t>
+          <t>3,12; 51,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 26,48</t>
+          <t>-14,5; 27,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 39,07</t>
+          <t>-14,47; 34,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,33; 87,82</t>
+          <t>-51,5; 84,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 319,6</t>
+          <t>5,06; 273,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,57; 82,43</t>
+          <t>-27,24; 84,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-59,81; 795,87</t>
+          <t>-63,71; 527,01</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 19,25</t>
+          <t>-19,41; 19,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 12,54</t>
+          <t>-27,23; 11,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 36,84</t>
+          <t>0,12; 37,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 26,55</t>
+          <t>-20,69; 25,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,24; 88,79</t>
+          <t>-53,96; 88,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,7; 55,21</t>
+          <t>-70,17; 52,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 109,14</t>
+          <t>0,51; 113,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 106,65</t>
+          <t>-37,35; 92,9</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-39,39; 3,57</t>
+          <t>-41,17; 2,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 36,27</t>
+          <t>-9,83; 40,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 20,49</t>
+          <t>-33,27; 19,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 30,48</t>
+          <t>4,07; 30,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-89,48; 34,59</t>
+          <t>-90,4; 31,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,81; 544,13</t>
+          <t>-58,77; 691,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,35; 583,52</t>
+          <t>18,96; 665,05</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 12,97</t>
+          <t>-21,9; 15,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 43,82</t>
+          <t>-6,09; 38,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 24,44</t>
+          <t>-28,32; 22,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,51; 17,6</t>
+          <t>-58,22; 19,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-87,32; 128,59</t>
+          <t>-84,55; 148,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 277,09</t>
+          <t>-19,97; 215,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,27; 69,26</t>
+          <t>-47,16; 59,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,04; 41,44</t>
+          <t>-79,69; 45,26</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-35,89; 44,17</t>
+          <t>-37,8; 37,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 64,79</t>
+          <t>1,3; 64,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-49,66; 46,57</t>
+          <t>-51,9; 52,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 34,87</t>
+          <t>-13,22; 34,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 248,8</t>
+          <t>-100,0; 195,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-74,7; 152,41</t>
+          <t>-77,37; 169,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-59,29; 648,17</t>
+          <t>-64,85; 677,75</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,33; -10,31</t>
+          <t>-52,98; -10,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 33,95</t>
+          <t>-13,39; 35,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,31; 51,27</t>
+          <t>-34,94; 47,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 19,38</t>
+          <t>-15,37; 20,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -14,25</t>
+          <t>-100,0; -5,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,14; 356,54</t>
+          <t>-67,17; 386,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,8; 180,73</t>
+          <t>-70,62; 178,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,79; 126,96</t>
+          <t>-45,74; 147,0</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 18,9</t>
+          <t>-14,19; 20,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 27,71</t>
+          <t>-4,98; 27,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 16,8</t>
+          <t>-16,74; 17,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 31,94</t>
+          <t>4,15; 31,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-40,64; 87,92</t>
+          <t>-42,81; 93,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 330,41</t>
+          <t>-25,42; 328,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-43,74; 72,76</t>
+          <t>-43,63; 73,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,56; 229,06</t>
+          <t>14,67; 230,7</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 31,88</t>
+          <t>-0,7; 32,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 26,99</t>
+          <t>-19,3; 27,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,98; 8,07</t>
+          <t>-37,52; 9,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 8,59</t>
+          <t>-29,15; 7,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 117,8</t>
+          <t>-1,91; 115,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,72; 112,69</t>
+          <t>-49,37; 121,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-90,63; 39,38</t>
+          <t>-88,92; 38,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 14,81</t>
+          <t>-38,45; 10,51</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 8,23</t>
+          <t>-8,31; 6,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,61; 18,66</t>
+          <t>2,58; 18,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 12,36</t>
+          <t>-6,82; 10,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 12,81</t>
+          <t>-7,46; 13,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 30,33</t>
+          <t>-24,54; 22,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,93; 90,77</t>
+          <t>9,93; 90,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 35,28</t>
+          <t>-16,05; 30,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 41,7</t>
+          <t>-19,01; 43,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6903-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6903-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,46</t>
+          <t>10,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>72,88%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 24,6</t>
+          <t>-26,51; 24,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 51,92</t>
+          <t>1,7; 51,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 27,92</t>
+          <t>-14,41; 27,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 34,37</t>
+          <t>-10,22; 32,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,5; 84,81</t>
+          <t>-56,53; 83,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 273,52</t>
+          <t>3,45; 285,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 84,56</t>
+          <t>-30,27; 85,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-63,71; 527,01</t>
+          <t>-58,0; 648,71</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,73</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 19,51</t>
+          <t>-18,26; 19,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 11,41</t>
+          <t>-28,36; 12,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 37,46</t>
+          <t>-0,18; 38,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 25,11</t>
+          <t>-17,78; 25,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,96; 88,6</t>
+          <t>-52,8; 83,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,17; 52,76</t>
+          <t>-73,68; 55,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 113,48</t>
+          <t>-0,79; 118,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 92,9</t>
+          <t>-32,54; 95,23</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,78</t>
+          <t>16,58</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>161,0%</t>
+          <t>160,51%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 2,35</t>
+          <t>-41,1; 2,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 40,68</t>
+          <t>-10,51; 38,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 19,54</t>
+          <t>-31,17; 18,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 30,88</t>
+          <t>4,97; 30,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-90,4; 31,03</t>
+          <t>-90,82; 24,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,77; 691,35</t>
+          <t>-57,66; 646,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,96; 665,05</t>
+          <t>11,14; 686,82</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-13,82</t>
+          <t>6,62</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-27,19%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 15,24</t>
+          <t>-21,61; 16,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 38,92</t>
+          <t>-5,87; 41,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 22,18</t>
+          <t>-26,9; 26,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,22; 19,45</t>
+          <t>-14,48; 28,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,55; 148,27</t>
+          <t>-84,77; 131,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 215,49</t>
+          <t>-15,85; 256,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,16; 59,3</t>
+          <t>-43,72; 71,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,69; 45,26</t>
+          <t>-21,66; 73,16</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,51</t>
+          <t>13,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-37,8; 37,74</t>
+          <t>-33,09; 47,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 64,47</t>
+          <t>0,29; 62,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-51,9; 52,94</t>
+          <t>-47,46; 45,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 34,54</t>
+          <t>-6,84; 36,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 195,62</t>
+          <t>-100,0; 284,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-77,37; 169,01</t>
+          <t>-72,3; 139,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-64,85; 677,75</t>
+          <t>-49,41; 781,08</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,65</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,98; -10,3</t>
+          <t>-52,95; -6,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 35,92</t>
+          <t>-13,05; 40,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,94; 47,37</t>
+          <t>-36,99; 51,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 20,97</t>
+          <t>-15,5; 21,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -5,2</t>
+          <t>-100,0; 20,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,17; 386,38</t>
+          <t>-69,01; 371,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,62; 178,48</t>
+          <t>-70,9; 180,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,74; 147,0</t>
+          <t>-44,04; 138,52</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,82</t>
+          <t>15,79</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>65,24%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 20,75</t>
+          <t>-14,61; 19,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 27,45</t>
+          <t>-6,37; 25,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 17,07</t>
+          <t>-16,77; 17,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 31,79</t>
+          <t>0,85; 28,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-42,81; 93,66</t>
+          <t>-42,04; 94,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 328,53</t>
+          <t>-32,46; 293,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-43,63; 73,71</t>
+          <t>-45,55; 76,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,67; 230,7</t>
+          <t>-2,9; 179,13</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-11,4</t>
+          <t>-15,88</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-16,15%</t>
+          <t>-22,54%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 32,62</t>
+          <t>0,52; 34,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 27,42</t>
+          <t>-21,27; 26,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,52; 9,06</t>
+          <t>-37,67; 12,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 7,08</t>
+          <t>-32,15; 2,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 115,28</t>
+          <t>0,94; 126,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,37; 121,23</t>
+          <t>-53,33; 110,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-88,92; 38,61</t>
+          <t>-88,94; 54,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-38,45; 10,51</t>
+          <t>-41,34; 3,46</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>6,63</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 6,57</t>
+          <t>-8,59; 6,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,58; 18,79</t>
+          <t>2,07; 19,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 10,76</t>
+          <t>-6,24; 11,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 13,31</t>
+          <t>-1,68; 13,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 22,58</t>
+          <t>-25,27; 23,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,93; 90,61</t>
+          <t>7,63; 94,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 30,3</t>
+          <t>-13,89; 33,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 43,48</t>
+          <t>-4,31; 42,85</t>
         </is>
       </c>
     </row>
